--- a/pic/PS/Table-Analysis.xlsx
+++ b/pic/PS/Table-Analysis.xlsx
@@ -4450,34 +4450,34 @@
                 <c:formatCode>0.000_ </c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>18.234</c:v>
+                  <c:v>18.943</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30.127</c:v>
+                  <c:v>32.175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>39.703</c:v>
+                  <c:v>42.184</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.299</c:v>
+                  <c:v>50.448</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.591</c:v>
+                  <c:v>56.027</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>60.121</c:v>
+                  <c:v>59.483</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62.467</c:v>
+                  <c:v>61.268</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>64.498</c:v>
+                  <c:v>62.862</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>66.208</c:v>
+                  <c:v>64.13</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>67.718</c:v>
+                  <c:v>65.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4563,34 +4563,34 @@
                 <c:formatCode>0.000_ </c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>30.639</c:v>
+                  <c:v>28.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34.25</c:v>
+                  <c:v>31.979</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.956</c:v>
+                  <c:v>40.452</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>57.299</c:v>
+                  <c:v>51.715</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.986</c:v>
+                  <c:v>60.278</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>78.276</c:v>
+                  <c:v>69.178</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>84.905</c:v>
+                  <c:v>74.676</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>87.328</c:v>
+                  <c:v>76.88</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>87.591</c:v>
+                  <c:v>77.012</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>85.187</c:v>
+                  <c:v>76.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5020,34 +5020,34 @@
                 <c:formatCode>0.000_ </c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.70542335790625</c:v>
+                  <c:v>5.2262560220234</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.42002992152162</c:v>
+                  <c:v>11.0698164069354</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.2641509433962</c:v>
+                  <c:v>9.39902434040814</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.9499746397911</c:v>
+                  <c:v>8.15844291458314</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.52307552037243</c:v>
+                  <c:v>7.72371621423618</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.47392391977491</c:v>
+                  <c:v>7.7679268684827</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.57580742962166</c:v>
+                  <c:v>7.82478801458635</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.49229325827637</c:v>
+                  <c:v>8.53456690574205</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.53093009012162</c:v>
+                  <c:v>9.11565748226366</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.37849103793247</c:v>
+                  <c:v>9.70756464996375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5129,34 +5129,34 @@
                 <c:formatCode>0.000_ </c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.94482227210292</c:v>
+                  <c:v>0.628447908929302</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.20485297796375</c:v>
+                  <c:v>1.98282451328627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.34456978050495</c:v>
+                  <c:v>3.32093622278002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.92417425655657</c:v>
+                  <c:v>6.65902617430436</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.98614650596869</c:v>
+                  <c:v>6.79386792685271</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.85603029129555</c:v>
+                  <c:v>5.27639319233015</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.37133550488599</c:v>
+                  <c:v>3.21675944418476</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.04265402843602</c:v>
+                  <c:v>0.0206773913403132</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.94516053433326</c:v>
+                  <c:v>3.95489459061938</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.78607399183155</c:v>
+                  <c:v>7.55061400597411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5565,34 +5565,34 @@
                 <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>160.31</c:v>
+                  <c:v>207.83</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>414.49</c:v>
+                  <c:v>415.73</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>413.35</c:v>
+                  <c:v>418.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>416.97</c:v>
+                  <c:v>419.81</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>408.79</c:v>
+                  <c:v>424.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>405.41</c:v>
+                  <c:v>426.91</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>426.8</c:v>
+                  <c:v>427.56</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>428.11</c:v>
+                  <c:v>428.22</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>428.77</c:v>
+                  <c:v>427.13</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>429.55</c:v>
+                  <c:v>425.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5677,31 +5677,31 @@
                   <c:v>400.64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400.73</c:v>
+                  <c:v>400.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>399.87</c:v>
+                  <c:v>399.58</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>399.58</c:v>
+                  <c:v>400.16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>399.87</c:v>
+                  <c:v>400.64</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>400.35</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>400.06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>400.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>400.06</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>400.06</c:v>
+                  <c:v>400.16</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>399.87</c:v>
+                  <c:v>400.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12288,7 +12288,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:Y69"/>
+  <dimension ref="B2:M69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="4" max="4" width="9.5"/>
@@ -12297,7 +12297,7 @@
     <col min="10" max="10" width="10.25"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25">
+    <row r="2" spans="2:13">
       <c r="B2">
         <v>10</v>
       </c>
@@ -12336,38 +12336,8 @@
       <c r="M2" s="2">
         <v>399.58</v>
       </c>
-      <c r="P2">
-        <v>10</v>
-      </c>
-      <c r="Q2">
-        <v>5</v>
-      </c>
-      <c r="R2">
-        <v>48.433</v>
-      </c>
-      <c r="S2">
-        <v>-43.52</v>
-      </c>
-      <c r="T2">
-        <v>17.89</v>
-      </c>
-      <c r="U2">
-        <v>46.081</v>
-      </c>
-      <c r="V2">
-        <v>61.713</v>
-      </c>
-      <c r="W2">
-        <v>-57.72</v>
-      </c>
-      <c r="X2">
-        <v>29.6</v>
-      </c>
-      <c r="Y2">
-        <v>399.58</v>
-      </c>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:13">
       <c r="B3">
         <v>20</v>
       </c>
@@ -12406,38 +12376,8 @@
       <c r="M3" s="2">
         <v>400.64</v>
       </c>
-      <c r="P3">
-        <v>20</v>
-      </c>
-      <c r="Q3">
-        <v>10</v>
-      </c>
-      <c r="R3">
-        <v>54.333</v>
-      </c>
-      <c r="S3">
-        <v>-65.593</v>
-      </c>
-      <c r="T3">
-        <v>30.809</v>
-      </c>
-      <c r="U3">
-        <v>417.5</v>
-      </c>
-      <c r="V3">
-        <v>68.786</v>
-      </c>
-      <c r="W3">
-        <v>-62.72</v>
-      </c>
-      <c r="X3">
-        <v>33.171</v>
-      </c>
-      <c r="Y3">
-        <v>400.64</v>
-      </c>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:13">
       <c r="B4">
         <v>30</v>
       </c>
@@ -12476,38 +12416,8 @@
       <c r="M4" s="2">
         <v>398.62</v>
       </c>
-      <c r="P4">
-        <v>30</v>
-      </c>
-      <c r="Q4">
-        <v>15</v>
-      </c>
-      <c r="R4">
-        <v>64.113</v>
-      </c>
-      <c r="S4">
-        <v>-80.666</v>
-      </c>
-      <c r="T4">
-        <v>39.187</v>
-      </c>
-      <c r="U4">
-        <v>409.8</v>
-      </c>
-      <c r="V4">
-        <v>79.44</v>
-      </c>
-      <c r="W4">
-        <v>-72.586</v>
-      </c>
-      <c r="X4">
-        <v>43.001</v>
-      </c>
-      <c r="Y4">
-        <v>398.62</v>
-      </c>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:13">
       <c r="B5">
         <v>40</v>
       </c>
@@ -12546,38 +12456,8 @@
       <c r="M5" s="2">
         <v>401.6</v>
       </c>
-      <c r="P5">
-        <v>40</v>
-      </c>
-      <c r="Q5">
-        <v>20</v>
-      </c>
-      <c r="R5">
-        <v>76</v>
-      </c>
-      <c r="S5">
-        <v>-92.633</v>
-      </c>
-      <c r="T5">
-        <v>46.598</v>
-      </c>
-      <c r="U5">
-        <v>409.39</v>
-      </c>
-      <c r="V5">
-        <v>97.88</v>
-      </c>
-      <c r="W5">
-        <v>-85.366</v>
-      </c>
-      <c r="X5">
-        <v>55.341</v>
-      </c>
-      <c r="Y5">
-        <v>401.6</v>
-      </c>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:13">
       <c r="B6">
         <v>50</v>
       </c>
@@ -12616,38 +12496,8 @@
       <c r="M6" s="2">
         <v>399.68</v>
       </c>
-      <c r="P6">
-        <v>50</v>
-      </c>
-      <c r="Q6">
-        <v>25</v>
-      </c>
-      <c r="R6">
-        <v>92.686</v>
-      </c>
-      <c r="S6">
-        <v>-107.88</v>
-      </c>
-      <c r="T6">
-        <v>55.419</v>
-      </c>
-      <c r="U6">
-        <v>422.36</v>
-      </c>
-      <c r="V6">
-        <v>112.08</v>
-      </c>
-      <c r="W6">
-        <v>-96.84</v>
-      </c>
-      <c r="X6">
-        <v>65.243</v>
-      </c>
-      <c r="Y6">
-        <v>399.68</v>
-      </c>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:13">
       <c r="B7">
         <v>60</v>
       </c>
@@ -12686,38 +12536,8 @@
       <c r="M7" s="2">
         <v>400.06</v>
       </c>
-      <c r="P7">
-        <v>60</v>
-      </c>
-      <c r="Q7">
-        <v>30</v>
-      </c>
-      <c r="R7">
-        <v>100.17</v>
-      </c>
-      <c r="S7">
-        <v>-114.43</v>
-      </c>
-      <c r="T7">
-        <v>59.244</v>
-      </c>
-      <c r="U7">
-        <v>426.8</v>
-      </c>
-      <c r="V7">
-        <v>123.01</v>
-      </c>
-      <c r="W7">
-        <v>-109.08</v>
-      </c>
-      <c r="X7">
-        <v>74.953</v>
-      </c>
-      <c r="Y7">
-        <v>400.06</v>
-      </c>
     </row>
-    <row r="8" spans="2:25">
+    <row r="8" spans="2:13">
       <c r="B8">
         <v>70</v>
       </c>
@@ -12756,38 +12576,8 @@
       <c r="M8" s="2">
         <v>399.87</v>
       </c>
-      <c r="P8">
-        <v>70</v>
-      </c>
-      <c r="Q8">
-        <v>35</v>
-      </c>
-      <c r="R8">
-        <v>104.43</v>
-      </c>
-      <c r="S8">
-        <v>-120.08</v>
-      </c>
-      <c r="T8">
-        <v>61.409</v>
-      </c>
-      <c r="U8">
-        <v>427.46</v>
-      </c>
-      <c r="V8">
-        <v>126.23</v>
-      </c>
-      <c r="W8">
-        <v>-120.11</v>
-      </c>
-      <c r="X8">
-        <v>80.381</v>
-      </c>
-      <c r="Y8">
-        <v>399.87</v>
-      </c>
     </row>
-    <row r="9" spans="2:25">
+    <row r="9" spans="2:13">
       <c r="B9">
         <v>80</v>
       </c>
@@ -12826,38 +12616,8 @@
       <c r="M9" s="2">
         <v>399.87</v>
       </c>
-      <c r="P9">
-        <v>80</v>
-      </c>
-      <c r="Q9">
-        <v>40</v>
-      </c>
-      <c r="R9">
-        <v>109.78</v>
-      </c>
-      <c r="S9">
-        <v>-124.92</v>
-      </c>
-      <c r="T9">
-        <v>63.326</v>
-      </c>
-      <c r="U9">
-        <v>425.71</v>
-      </c>
-      <c r="V9">
-        <v>126.28</v>
-      </c>
-      <c r="W9">
-        <v>-124.92</v>
-      </c>
-      <c r="X9">
-        <v>82.718</v>
-      </c>
-      <c r="Y9">
-        <v>399.87</v>
-      </c>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:13">
       <c r="B10">
         <v>90</v>
       </c>
@@ -12896,38 +12656,8 @@
       <c r="M10" s="2">
         <v>399.87</v>
       </c>
-      <c r="P10">
-        <v>90</v>
-      </c>
-      <c r="Q10">
-        <v>45</v>
-      </c>
-      <c r="R10">
-        <v>113.34</v>
-      </c>
-      <c r="S10">
-        <v>-128.69</v>
-      </c>
-      <c r="T10">
-        <v>64.916</v>
-      </c>
-      <c r="U10">
-        <v>424.95</v>
-      </c>
-      <c r="V10">
-        <v>127.27</v>
-      </c>
-      <c r="W10">
-        <v>-133.99</v>
-      </c>
-      <c r="X10">
-        <v>83.515</v>
-      </c>
-      <c r="Y10">
-        <v>399.87</v>
-      </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:13">
       <c r="B11">
         <v>100</v>
       </c>
@@ -12964,36 +12694,6 @@
         <v>4.75184794086589</v>
       </c>
       <c r="M11" s="2">
-        <v>400.06</v>
-      </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-      <c r="Q11">
-        <v>50</v>
-      </c>
-      <c r="R11">
-        <v>117.35</v>
-      </c>
-      <c r="S11">
-        <v>-134.07</v>
-      </c>
-      <c r="T11">
-        <v>66.18</v>
-      </c>
-      <c r="U11">
-        <v>424.95</v>
-      </c>
-      <c r="V11">
-        <v>126.28</v>
-      </c>
-      <c r="W11">
-        <v>-138.88</v>
-      </c>
-      <c r="X11">
-        <v>81.67</v>
-      </c>
-      <c r="Y11">
         <v>400.06</v>
       </c>
     </row>
@@ -13471,33 +13171,33 @@
         <v>5</v>
       </c>
       <c r="D2" s="1">
-        <v>48.273</v>
+        <v>48.926</v>
       </c>
       <c r="E2" s="1">
-        <v>-42.206</v>
+        <v>-44.066</v>
       </c>
       <c r="F2" s="1">
-        <v>18.234</v>
+        <v>18.943</v>
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G11" si="0">ABS(ABS(D2)-ABS(E2))/(ABS(D2)+ABS(E2))*100</f>
-        <v>6.70542335790625</v>
+        <v>5.2262560220234</v>
       </c>
       <c r="H2" s="2">
-        <v>160.31</v>
+        <v>207.83</v>
       </c>
       <c r="I2" s="1">
-        <v>61.456</v>
+        <v>60.286</v>
       </c>
       <c r="J2" s="1">
-        <v>-57.94</v>
+        <v>-59.533</v>
       </c>
       <c r="K2" s="1">
-        <v>30.639</v>
+        <v>28.05</v>
       </c>
       <c r="L2" s="1">
         <f t="shared" ref="L2:L11" si="1">ABS(ABS(I2)-ABS(J2))/(ABS(I2)+ABS(J2))*100</f>
-        <v>2.94482227210292</v>
+        <v>0.628447908929302</v>
       </c>
       <c r="M2" s="2">
         <v>400.64</v>
@@ -13511,36 +13211,36 @@
         <v>10</v>
       </c>
       <c r="D3" s="1">
-        <v>51.766</v>
+        <v>55.753</v>
       </c>
       <c r="E3" s="1">
-        <v>-62.533</v>
+        <v>-69.633</v>
       </c>
       <c r="F3" s="1">
-        <v>30.127</v>
+        <v>32.175</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>9.42002992152162</v>
+        <v>11.0698164069354</v>
       </c>
       <c r="H3" s="2">
-        <v>414.49</v>
+        <v>415.73</v>
       </c>
       <c r="I3" s="1">
-        <v>68.733</v>
+        <v>68.046</v>
       </c>
       <c r="J3" s="1">
-        <v>-63.186</v>
+        <v>-65.4</v>
       </c>
       <c r="K3" s="1">
-        <v>34.25</v>
+        <v>31.979</v>
       </c>
       <c r="L3" s="1">
         <f t="shared" si="1"/>
-        <v>4.20485297796375</v>
+        <v>1.98282451328627</v>
       </c>
       <c r="M3" s="2">
-        <v>400.73</v>
+        <v>400.16</v>
       </c>
     </row>
     <row r="4" spans="2:13">
@@ -13551,36 +13251,36 @@
         <v>15</v>
       </c>
       <c r="D4" s="1">
-        <v>61.38</v>
+        <v>70.946</v>
       </c>
       <c r="E4" s="1">
-        <v>-78.54</v>
+        <v>-85.666</v>
       </c>
       <c r="F4" s="1">
-        <v>39.703</v>
+        <v>42.184</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>12.2641509433962</v>
+        <v>9.39902434040814</v>
       </c>
       <c r="H4" s="2">
-        <v>413.35</v>
+        <v>418.55</v>
       </c>
       <c r="I4" s="1">
-        <v>79.413</v>
+        <v>78.62</v>
       </c>
       <c r="J4" s="1">
-        <v>-72.8</v>
+        <v>-73.566</v>
       </c>
       <c r="K4" s="1">
-        <v>43.956</v>
+        <v>40.452</v>
       </c>
       <c r="L4" s="1">
         <f t="shared" si="1"/>
-        <v>4.34456978050495</v>
+        <v>3.32093622278002</v>
       </c>
       <c r="M4" s="2">
-        <v>399.87</v>
+        <v>399.58</v>
       </c>
     </row>
     <row r="5" spans="2:13">
@@ -13591,36 +13291,36 @@
         <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>71.106</v>
+        <v>85.313</v>
       </c>
       <c r="E5" s="1">
-        <v>-88.593</v>
+        <v>-100.47</v>
       </c>
       <c r="F5" s="1">
-        <v>46.299</v>
+        <v>50.448</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>10.9499746397911</v>
+        <v>8.15844291458314</v>
       </c>
       <c r="H5" s="2">
-        <v>416.97</v>
+        <v>419.81</v>
       </c>
       <c r="I5" s="1">
-        <v>97.44</v>
+        <v>94.926</v>
       </c>
       <c r="J5" s="1">
-        <v>-84.82</v>
+        <v>-83.073</v>
       </c>
       <c r="K5" s="1">
-        <v>57.299</v>
+        <v>51.715</v>
       </c>
       <c r="L5" s="1">
         <f t="shared" si="1"/>
-        <v>6.92417425655657</v>
+        <v>6.65902617430436</v>
       </c>
       <c r="M5" s="2">
-        <v>399.58</v>
+        <v>400.16</v>
       </c>
     </row>
     <row r="6" spans="2:13">
@@ -13631,36 +13331,36 @@
         <v>25</v>
       </c>
       <c r="D6" s="1">
-        <v>86.213</v>
+        <v>94.466</v>
       </c>
       <c r="E6" s="1">
-        <v>-100.24</v>
+        <v>-110.28</v>
       </c>
       <c r="F6" s="1">
-        <v>55.591</v>
+        <v>56.027</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>7.52307552037243</v>
+        <v>7.72371621423618</v>
       </c>
       <c r="H6" s="2">
-        <v>408.79</v>
+        <v>424.08</v>
       </c>
       <c r="I6" s="1">
-        <v>111.67</v>
+        <v>108.36</v>
       </c>
       <c r="J6" s="1">
-        <v>-97.086</v>
+        <v>-94.573</v>
       </c>
       <c r="K6" s="1">
-        <v>67.986</v>
+        <v>60.278</v>
       </c>
       <c r="L6" s="1">
         <f t="shared" si="1"/>
-        <v>6.98614650596869</v>
+        <v>6.79386792685271</v>
       </c>
       <c r="M6" s="2">
-        <v>399.87</v>
+        <v>400.64</v>
       </c>
     </row>
     <row r="7" spans="2:13">
@@ -13671,36 +13371,36 @@
         <v>30</v>
       </c>
       <c r="D7" s="1">
-        <v>94.873</v>
+        <v>100.39</v>
       </c>
       <c r="E7" s="1">
-        <v>-110.2</v>
+        <v>-117.3</v>
       </c>
       <c r="F7" s="1">
-        <v>60.121</v>
+        <v>59.483</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>7.47392391977491</v>
+        <v>7.7679268684827</v>
       </c>
       <c r="H7" s="2">
-        <v>405.41</v>
+        <v>426.91</v>
       </c>
       <c r="I7" s="1">
-        <v>123.01</v>
+        <v>117.22</v>
       </c>
       <c r="J7" s="1">
-        <v>-109.4</v>
+        <v>-105.47</v>
       </c>
       <c r="K7" s="1">
-        <v>78.276</v>
+        <v>69.178</v>
       </c>
       <c r="L7" s="1">
         <f t="shared" si="1"/>
-        <v>5.85603029129555</v>
+        <v>5.27639319233015</v>
       </c>
       <c r="M7" s="2">
-        <v>400.06</v>
+        <v>400.35</v>
       </c>
     </row>
     <row r="8" spans="2:13">
@@ -13711,36 +13411,36 @@
         <v>35</v>
       </c>
       <c r="D8" s="1">
-        <v>98.313</v>
+        <v>104.9</v>
       </c>
       <c r="E8" s="1">
-        <v>-114.43</v>
+        <v>-122.71</v>
       </c>
       <c r="F8" s="1">
-        <v>62.467</v>
+        <v>61.268</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>7.57580742962166</v>
+        <v>7.82478801458635</v>
       </c>
       <c r="H8" s="2">
-        <v>426.8</v>
+        <v>427.56</v>
       </c>
       <c r="I8" s="1">
-        <v>126.94</v>
+        <v>121.45</v>
       </c>
       <c r="J8" s="1">
-        <v>-118.66</v>
+        <v>-113.88</v>
       </c>
       <c r="K8" s="1">
-        <v>84.905</v>
+        <v>74.676</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="1"/>
-        <v>3.37133550488599</v>
+        <v>3.21675944418476</v>
       </c>
       <c r="M8" s="2">
-        <v>400.25</v>
+        <v>400.06</v>
       </c>
     </row>
     <row r="9" spans="2:13">
@@ -13751,33 +13451,33 @@
         <v>40</v>
       </c>
       <c r="D9" s="1">
-        <v>103.53</v>
+        <v>107.76</v>
       </c>
       <c r="E9" s="1">
-        <v>-120.3</v>
+        <v>-127.87</v>
       </c>
       <c r="F9" s="1">
-        <v>64.498</v>
+        <v>62.862</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="0"/>
-        <v>7.49229325827637</v>
+        <v>8.53456690574205</v>
       </c>
       <c r="H9" s="2">
-        <v>428.11</v>
+        <v>428.22</v>
       </c>
       <c r="I9" s="1">
-        <v>127.92</v>
+        <v>120.93</v>
       </c>
       <c r="J9" s="1">
-        <v>-125.28</v>
+        <v>-120.88</v>
       </c>
       <c r="K9" s="1">
-        <v>87.328</v>
+        <v>76.88</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="1"/>
-        <v>1.04265402843602</v>
+        <v>0.0206773913403132</v>
       </c>
       <c r="M9" s="2">
         <v>400.06</v>
@@ -13791,36 +13491,36 @@
         <v>45</v>
       </c>
       <c r="D10" s="1">
-        <v>104.54</v>
+        <v>110.17</v>
       </c>
       <c r="E10" s="1">
-        <v>-124.04</v>
+        <v>-132.27</v>
       </c>
       <c r="F10" s="1">
-        <v>66.208</v>
+        <v>64.13</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>8.53093009012162</v>
+        <v>9.11565748226366</v>
       </c>
       <c r="H10" s="2">
-        <v>428.77</v>
+        <v>427.13</v>
       </c>
       <c r="I10" s="1">
-        <v>125.52</v>
+        <v>117.54</v>
       </c>
       <c r="J10" s="1">
-        <v>-130.5</v>
+        <v>127.22</v>
       </c>
       <c r="K10" s="1">
-        <v>87.591</v>
+        <v>77.012</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="1"/>
-        <v>1.94516053433326</v>
+        <v>3.95489459061938</v>
       </c>
       <c r="M10" s="2">
-        <v>400.06</v>
+        <v>400.16</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -13831,36 +13531,36 @@
         <v>50</v>
       </c>
       <c r="D11" s="1">
-        <v>109.9</v>
+        <v>112.08</v>
       </c>
       <c r="E11" s="1">
-        <v>-130</v>
+        <v>-136.18</v>
       </c>
       <c r="F11" s="1">
-        <v>67.718</v>
+        <v>65.2</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>8.37849103793247</v>
+        <v>9.70756464996375</v>
       </c>
       <c r="H11" s="2">
-        <v>429.55</v>
+        <v>425.71</v>
       </c>
       <c r="I11" s="1">
-        <v>120.06</v>
+        <v>111.42</v>
       </c>
       <c r="J11" s="1">
-        <v>-132.13</v>
+        <v>-129.62</v>
       </c>
       <c r="K11" s="1">
-        <v>85.187</v>
+        <v>76.42</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>4.78607399183155</v>
+        <v>7.55061400597411</v>
       </c>
       <c r="M11" s="2">
-        <v>399.87</v>
+        <v>400.64</v>
       </c>
     </row>
     <row r="12" spans="4:13">
@@ -13904,11 +13604,11 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" ref="C15:C24" si="2">F2</f>
-        <v>18.234</v>
+        <v>18.943</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" ref="D15:D24" si="3">K2</f>
-        <v>30.639</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -13917,11 +13617,11 @@
       </c>
       <c r="C16" s="1">
         <f t="shared" si="2"/>
-        <v>30.127</v>
+        <v>32.175</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="3"/>
-        <v>34.25</v>
+        <v>31.979</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -13930,11 +13630,11 @@
       </c>
       <c r="C17" s="1">
         <f t="shared" si="2"/>
-        <v>39.703</v>
+        <v>42.184</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="3"/>
-        <v>43.956</v>
+        <v>40.452</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -13943,11 +13643,11 @@
       </c>
       <c r="C18" s="1">
         <f t="shared" si="2"/>
-        <v>46.299</v>
+        <v>50.448</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="3"/>
-        <v>57.299</v>
+        <v>51.715</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -13956,11 +13656,11 @@
       </c>
       <c r="C19" s="1">
         <f t="shared" si="2"/>
-        <v>55.591</v>
+        <v>56.027</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="3"/>
-        <v>67.986</v>
+        <v>60.278</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -13969,11 +13669,11 @@
       </c>
       <c r="C20" s="1">
         <f t="shared" si="2"/>
-        <v>60.121</v>
+        <v>59.483</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="3"/>
-        <v>78.276</v>
+        <v>69.178</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -13982,11 +13682,11 @@
       </c>
       <c r="C21" s="1">
         <f t="shared" si="2"/>
-        <v>62.467</v>
+        <v>61.268</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="3"/>
-        <v>84.905</v>
+        <v>74.676</v>
       </c>
     </row>
     <row r="22" spans="2:4">
@@ -13995,11 +13695,11 @@
       </c>
       <c r="C22" s="1">
         <f t="shared" si="2"/>
-        <v>64.498</v>
+        <v>62.862</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" si="3"/>
-        <v>87.328</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -14008,11 +13708,11 @@
       </c>
       <c r="C23" s="1">
         <f t="shared" si="2"/>
-        <v>66.208</v>
+        <v>64.13</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="3"/>
-        <v>87.591</v>
+        <v>77.012</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -14021,11 +13721,11 @@
       </c>
       <c r="C24" s="1">
         <f t="shared" si="2"/>
-        <v>67.718</v>
+        <v>65.2</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" si="3"/>
-        <v>85.187</v>
+        <v>76.42</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -14045,11 +13745,11 @@
       </c>
       <c r="C37" s="1">
         <f t="shared" ref="C37:C46" si="4">G2</f>
-        <v>6.70542335790625</v>
+        <v>5.2262560220234</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" ref="D37:D46" si="5">L2</f>
-        <v>2.94482227210292</v>
+        <v>0.628447908929302</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -14058,11 +13758,11 @@
       </c>
       <c r="C38" s="1">
         <f t="shared" si="4"/>
-        <v>9.42002992152162</v>
+        <v>11.0698164069354</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="5"/>
-        <v>4.20485297796375</v>
+        <v>1.98282451328627</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -14071,11 +13771,11 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" si="4"/>
-        <v>12.2641509433962</v>
+        <v>9.39902434040814</v>
       </c>
       <c r="D39" s="1">
         <f t="shared" si="5"/>
-        <v>4.34456978050495</v>
+        <v>3.32093622278002</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -14084,11 +13784,11 @@
       </c>
       <c r="C40" s="1">
         <f t="shared" si="4"/>
-        <v>10.9499746397911</v>
+        <v>8.15844291458314</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" si="5"/>
-        <v>6.92417425655657</v>
+        <v>6.65902617430436</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -14097,11 +13797,11 @@
       </c>
       <c r="C41" s="1">
         <f t="shared" si="4"/>
-        <v>7.52307552037243</v>
+        <v>7.72371621423618</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="5"/>
-        <v>6.98614650596869</v>
+        <v>6.79386792685271</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -14110,11 +13810,11 @@
       </c>
       <c r="C42" s="1">
         <f t="shared" si="4"/>
-        <v>7.47392391977491</v>
+        <v>7.7679268684827</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" si="5"/>
-        <v>5.85603029129555</v>
+        <v>5.27639319233015</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -14123,11 +13823,11 @@
       </c>
       <c r="C43" s="1">
         <f t="shared" si="4"/>
-        <v>7.57580742962166</v>
+        <v>7.82478801458635</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" si="5"/>
-        <v>3.37133550488599</v>
+        <v>3.21675944418476</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -14136,11 +13836,11 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" si="4"/>
-        <v>7.49229325827637</v>
+        <v>8.53456690574205</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" si="5"/>
-        <v>1.04265402843602</v>
+        <v>0.0206773913403132</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -14149,11 +13849,11 @@
       </c>
       <c r="C45" s="1">
         <f t="shared" si="4"/>
-        <v>8.53093009012162</v>
+        <v>9.11565748226366</v>
       </c>
       <c r="D45" s="1">
         <f t="shared" si="5"/>
-        <v>1.94516053433326</v>
+        <v>3.95489459061938</v>
       </c>
     </row>
     <row r="46" spans="2:4">
@@ -14162,11 +13862,11 @@
       </c>
       <c r="C46" s="1">
         <f t="shared" si="4"/>
-        <v>8.37849103793247</v>
+        <v>9.70756464996375</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" si="5"/>
-        <v>4.78607399183155</v>
+        <v>7.55061400597411</v>
       </c>
     </row>
     <row r="59" spans="2:4">
@@ -14186,7 +13886,7 @@
       </c>
       <c r="C60" s="2">
         <f t="shared" ref="C60:C69" si="6">H2</f>
-        <v>160.31</v>
+        <v>207.83</v>
       </c>
       <c r="D60" s="2">
         <f t="shared" ref="D60:D69" si="7">M2</f>
@@ -14199,11 +13899,11 @@
       </c>
       <c r="C61" s="2">
         <f t="shared" si="6"/>
-        <v>414.49</v>
+        <v>415.73</v>
       </c>
       <c r="D61" s="2">
         <f t="shared" si="7"/>
-        <v>400.73</v>
+        <v>400.16</v>
       </c>
     </row>
     <row r="62" spans="2:4">
@@ -14212,11 +13912,11 @@
       </c>
       <c r="C62" s="2">
         <f t="shared" si="6"/>
-        <v>413.35</v>
+        <v>418.55</v>
       </c>
       <c r="D62" s="2">
         <f t="shared" si="7"/>
-        <v>399.87</v>
+        <v>399.58</v>
       </c>
     </row>
     <row r="63" spans="2:4">
@@ -14225,11 +13925,11 @@
       </c>
       <c r="C63" s="2">
         <f t="shared" si="6"/>
-        <v>416.97</v>
+        <v>419.81</v>
       </c>
       <c r="D63" s="2">
         <f t="shared" si="7"/>
-        <v>399.58</v>
+        <v>400.16</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -14238,11 +13938,11 @@
       </c>
       <c r="C64" s="2">
         <f t="shared" si="6"/>
-        <v>408.79</v>
+        <v>424.08</v>
       </c>
       <c r="D64" s="2">
         <f t="shared" si="7"/>
-        <v>399.87</v>
+        <v>400.64</v>
       </c>
     </row>
     <row r="65" spans="2:4">
@@ -14251,11 +13951,11 @@
       </c>
       <c r="C65" s="2">
         <f t="shared" si="6"/>
-        <v>405.41</v>
+        <v>426.91</v>
       </c>
       <c r="D65" s="2">
         <f t="shared" si="7"/>
-        <v>400.06</v>
+        <v>400.35</v>
       </c>
     </row>
     <row r="66" spans="2:4">
@@ -14264,11 +13964,11 @@
       </c>
       <c r="C66" s="2">
         <f t="shared" si="6"/>
-        <v>426.8</v>
+        <v>427.56</v>
       </c>
       <c r="D66" s="2">
         <f t="shared" si="7"/>
-        <v>400.25</v>
+        <v>400.06</v>
       </c>
     </row>
     <row r="67" spans="2:4">
@@ -14277,7 +13977,7 @@
       </c>
       <c r="C67" s="2">
         <f t="shared" si="6"/>
-        <v>428.11</v>
+        <v>428.22</v>
       </c>
       <c r="D67" s="2">
         <f t="shared" si="7"/>
@@ -14290,11 +13990,11 @@
       </c>
       <c r="C68" s="2">
         <f t="shared" si="6"/>
-        <v>428.77</v>
+        <v>427.13</v>
       </c>
       <c r="D68" s="2">
         <f t="shared" si="7"/>
-        <v>400.06</v>
+        <v>400.16</v>
       </c>
     </row>
     <row r="69" spans="2:4">
@@ -14303,11 +14003,11 @@
       </c>
       <c r="C69" s="2">
         <f t="shared" si="6"/>
-        <v>429.55</v>
+        <v>425.71</v>
       </c>
       <c r="D69" s="2">
         <f t="shared" si="7"/>
-        <v>399.87</v>
+        <v>400.64</v>
       </c>
     </row>
   </sheetData>
